--- a/stories/arbres/ATOM-SOC.TRA.002-02.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hugo et papa montent dans le bus. Papa montre la place. Hugo pose ses fesses sur le siège. Il est assis. Son dos est contre le dossier. Ses pieds sont sur le plancher. Papa s'assoit à côté. Papa, c'est l'adulte. Papa dit : on reste assis, avec l'adulte. Le bus roule. Les maisons défilent. Hugo tient son cartable. Il reste assis, avec papa. Le bus s'arrête. Hugo reste assis. Papa dit : maintenant on se lève. Ils descendent ensemble. Hugo donne la main.</t>
+          <t>Hugo et papa montent dans le bus. Papa montre la place. Hugo pose ses fesses sur le siège. Il est assis. Son dos est contre le dossier. Ses pieds sont sur le plancher. Papa s'assoit à côté. Papa, c'est l'adulte. On reste assis, avec l'adulte. Le bus roule. Les maisons défilent. Hugo tient son cartable. Il reste assis, avec papa. Le bus s'arrête. Hugo reste assis. Maintenant on se lève. Ils descendent ensemble. Hugo donne la main.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo et papa montent dans le bus. Papa montre la place. Hugo pose ses fesses sur le siège. Il est assis. Son dos est contre le dossier. Ses pieds sont sur le plancher. Papa s'assoit à côté. Papa, c'est l'adulte.
+papa|On reste assis, avec l'adulte.
+narrateur|Le bus roule. Les maisons défilent. Hugo tient son cartable. Il reste assis, avec papa. Le bus s'arrête. Hugo reste assis.
+papa|Maintenant on se lève. Ils descendent ensemble.
+narrateur|Hugo donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo est dans le bus. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1671,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo est resté assis. Papa, l'adulte, était à côté.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1842,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Ils marchent sur le trottoir. Hugo tient la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2009,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2049,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.TRA.002-02.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.002-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Hugo donne la main.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Hugo est dans le bus. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1683,7 @@
           <t>narrateur|Hugo est resté assis. Papa, l'adulte, était à côté.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1847,6 +1855,7 @@
           <t>narrateur|Ils marchent sur le trottoir. Hugo tient la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2014,6 +2023,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2032,7 +2042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2056,6 +2066,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2257,6 +2281,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.TRA.002-02.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hugo reste assis dans le bus</t>
+          <t>La buée du bus</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Raphaël veut dessiner sur la buée du bus. Premier arrêt : il reste assis. Au deuxième, papa et lui se lèvent ensemble.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hugo et papa montent dans le bus. Papa montre la place. Hugo pose ses fesses sur le siège. Il est assis. Son dos est contre le dossier. Ses pieds sont sur le plancher. Papa s'assoit à côté. Papa, c'est l'adulte. On reste assis, avec l'adulte. Le bus roule. Les maisons défilent. Hugo tient son cartable. Il reste assis, avec papa. Le bus s'arrête. Hugo reste assis. Maintenant on se lève. Ils descendent ensemble. Hugo donne la main.</t>
+          <t>La vitre du bus a un petit nuage. Le nuage, c'est de la buée tiède. Un ticket jaune sent encore l'encre. Le plancher du bus est mouillé par endroits. Raphaël vit ici, avec papa. Tu as vu la buée, Raphaël ? Oui. Je peux dessiner ? Oui. Assis, avec un adulte. En ce moment, ils montent dans le bus. Papa montre la place près de la vitre. Raphaël s'assoit. Son dos touche le dossier. On reste assis, avec l'adulte. D'accord. Le bus part. Les magasins glissent, flous. Raphaël trace un rond dans la buée. Un soleil. Il est beau. Tu restes assis, Raphaël ? Oui. Le soleil de buée s'efface un peu. Raphaël le redessine, assis. Le bus ralentit. Premier arrêt. Nous, on reste assis. Des gens descendent. Raphaël reste sur sa place. Le ticket jaune crisse dans sa main. On reste encore ? Oui. Jusqu'à notre arrêt. Raphaël redessine un rayon. La buée perle sous le doigt. Une goutte descend, toute lente. Ton soleil a une larme. C'est la buée. Le bus reprend, plus fort. Les magasins redeviennent nets. Raphaël reste sur le siège.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hugo et papa montent dans le bus. Papa montre la place. Hugo pose ses fesses sur le siège. Il est &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt;. Son dos est contre le dossier. Ses pieds sont sur le plancher. Papa s'assoit à côté. Papa, c'est l'adulte. Papa dit : on reste assis, avec l'adulte. Le bus roule. Les maisons défilent. Hugo tient son cartable. Il reste assis, avec papa. Le bus s'arrête. Hugo reste assis. Papa dit : maintenant on se lève. Ils descendent ensemble. Hugo donne la main.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La vitre du bus a un petit nuage. Le nuage, c'est de la buée tiède. Un ticket jaune sent encore l'encre. Le plancher du bus est mouillé par endroits. Raphaël vit ici, avec papa. Tu as vu la buée, Raphaël ? Oui. Je peux dessiner ? Oui. Assis, avec un adulte. En ce moment, ils montent dans le bus. Papa montre la place près de la vitre. Raphaël s'assoit. Son dos touche le dossier. On reste assis, avec l'adulte. D'accord. Le bus part. Les magasins glissent, flous. Raphaël trace un rond dans la buée. Un soleil. Il est beau. Tu restes assis, Raphaël ? Oui. Le soleil de buée s'efface un peu. Raphaël le redessine, assis. Le bus ralentit. Premier arrêt. Nous, on reste assis. Des gens descendent. Raphaël reste sur sa place. Le ticket jaune crisse dans sa main. On reste encore ? Oui. Jusqu'à notre arrêt. Raphaël redessine un rayon. La buée perle sous le doigt. Une goutte descend, toute lente. Ton soleil a une larme. C'est la buée. Le bus reprend, plus fort. Les magasins redeviennent nets. Raphaël reste sur le siège.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,14 +1324,50 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hugo et papa montent dans le bus. Papa montre la place. Hugo pose ses fesses sur le siège. Il est assis. Son dos est contre le dossier. Ses pieds sont sur le plancher. Papa s'assoit à côté. Papa, c'est l'adulte.
+          <t>narrateur|La vitre du bus a un petit nuage.
+narrateur|Le nuage, c'est de la buée tiède.
+narrateur|Un ticket jaune sent encore l'encre.
+narrateur|Le plancher du bus est mouillé par endroits.
+narrateur|Raphaël vit ici, avec papa.
+papa|Tu as vu la buée, Raphaël ?
+enfant-m|Oui.
+enfant-m|Je peux dessiner ?
+papa|Oui.
+papa|Assis, avec un adulte.
+narrateur|En ce moment, ils montent dans le bus.
+narrateur|Papa montre la place près de la vitre.
+narrateur|Raphaël s'assoit.
+narrateur|Son dos touche le dossier.
 papa|On reste assis, avec l'adulte.
-narrateur|Le bus roule. Les maisons défilent. Hugo tient son cartable. Il reste assis, avec papa. Le bus s'arrête. Hugo reste assis.
-papa|Maintenant on se lève. Ils descendent ensemble.
-narrateur|Hugo donne la main.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+enfant-m|D'accord.
+narrateur|Le bus part.
+narrateur|Les magasins glissent, flous.
+narrateur|Raphaël trace un rond dans la buée.
+enfant-m|Un soleil.
+papa|Il est beau.
+papa|Tu restes assis, Raphaël ?
+enfant-m|Oui.
+narrateur|Le soleil de buée s'efface un peu.
+narrateur|Raphaël le redessine, assis.
+narrateur|Le bus ralentit.
+papa|Premier arrêt.
+papa|Nous, on reste assis.
+narrateur|Des gens descendent.
+narrateur|Raphaël reste sur sa place.
+narrateur|Le ticket jaune crisse dans sa main.
+enfant-m|On reste encore ?
+papa|Oui.
+papa|Jusqu'à notre arrêt.
+narrateur|Raphaël redessine un rayon.
+narrateur|La buée perle sous le doigt.
+narrateur|Une goutte descend, toute lente.
+papa|Ton soleil a une larme.
+enfant-m|C'est la buée.
+narrateur|Le bus reprend, plus fort.
+narrateur|Les magasins redeviennent nets.
+narrateur|Raphaël reste sur le siège.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,12 +1392,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Hugo est dans le bus. Que fait-il ?</t>
+          <t>Raphaël est dans le bus. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Hugo est dans le bus. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël est dans le bus. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1379,7 +1427,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Ses fesses sont sur le siège. Avec qui ?</t>
+          <t>Sa place est sur le siège. Que fait Raphaël ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1428,7 +1476,7 @@
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1504,10 +1552,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Hugo est dans le bus. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Raphaël est dans le bus.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,12 +1580,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hugo est resté assis. Papa, l'adulte, était à côté.</t>
+          <t>Le bus repart. La buée revient sur la vitre. Je refais le soleil. Oui. Tu es resté assis. Bravo. Le doigt de Raphaël laisse un trait. Un peu d'eau coule vers le bas. Tu as froid au doigt ? Un peu. Papa pose sa main près de la sienne. Le bus ralentit encore. Deuxième arrêt. Celui-là, c'est le nôtre. Raphaël reste assis encore un instant. Maintenant on se lève. Ils se lèvent ensemble. Raphaël donne la main à papa. Le soleil de buée reste derrière. Il va s'effacer. Oui. Toi, tu as gardé ta place. Le plancher est encore un peu mouillé. Leurs pas font un bruit court.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Hugo est resté &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt;. Papa, l'adulte, était à côté.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le bus repart. La buée revient sur la vitre. Je refais le soleil. Oui. Tu es resté assis. Bravo. Le doigt de Raphaël laisse un trait. Un peu d'eau coule vers le bas. Tu as froid au doigt ? Un peu. Papa pose sa main près de la sienne. Le bus ralentit encore. Deuxième arrêt. Celui-là, c'est le nôtre. Raphaël reste assis encore un instant. Maintenant on se lève. Ils se lèvent ensemble. Raphaël donne la main à papa. Le soleil de buée reste derrière. Il va s'effacer. Oui. Toi, tu as gardé ta place. Le plancher est encore un peu mouillé. Leurs pas font un bruit court.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1593,7 +1641,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
@@ -1680,10 +1728,32 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hugo est resté assis. Papa, l'adulte, était à côté.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Le bus repart.
+narrateur|La buée revient sur la vitre.
+enfant-m|Je refais le soleil.
+papa|Oui.
+papa|Tu es resté assis.
+papa|Bravo.
+narrateur|Le doigt de Raphaël laisse un trait.
+narrateur|Un peu d'eau coule vers le bas.
+papa|Tu as froid au doigt ?
+enfant-m|Un peu.
+narrateur|Papa pose sa main près de la sienne.
+narrateur|Le bus ralentit encore.
+papa|Deuxième arrêt.
+papa|Celui-là, c'est le nôtre.
+narrateur|Raphaël reste assis encore un instant.
+papa|Maintenant on se lève.
+narrateur|Ils se lèvent ensemble.
+narrateur|Raphaël donne la main à papa.
+narrateur|Le soleil de buée reste derrière.
+enfant-m|Il va s'effacer.
+papa|Oui.
+papa|Toi, tu as gardé ta place.
+narrateur|Le plancher est encore un peu mouillé.
+narrateur|Leurs pas font un bruit court.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1708,12 +1778,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ils marchent sur le trottoir. Hugo tient la main.</t>
+          <t>Ils descendent sur le trottoir. L'air froid pique les joues. Mon soleil est resté là-bas. La buée le gardera un peu. Le bus repart, tout gris. Une trace de doigt brille encore. Tu as gardé ta place. Jusqu'à notre arrêt. Oui. Le ticket jaune est un peu froissé. Raphaël le met dans la poche de papa.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Ils marchent sur le &lt;emphasis level="moderate"&gt;trottoir&lt;/emphasis&gt;. Hugo tient la main.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ils descendent sur le trottoir. L'air froid pique les joues. Mon soleil est resté là-bas. La buée le gardera un peu. Le bus repart, tout gris. Une trace de doigt brille encore. Tu as gardé ta place. Jusqu'à notre arrêt. Oui. Le ticket jaune est un peu froissé. Raphaël le met dans la poche de papa.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1769,7 +1839,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
@@ -1852,10 +1922,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Ils marchent sur le trottoir. Hugo tient la main.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Ils descendent sur le trottoir.
+narrateur|L'air froid pique les joues.
+enfant-m|Mon soleil est resté là-bas.
+papa|La buée le gardera un peu.
+narrateur|Le bus repart, tout gris.
+narrateur|Une trace de doigt brille encore.
+papa|Tu as gardé ta place.
+enfant-m|Jusqu'à notre arrêt.
+papa|Oui.
+narrateur|Le ticket jaune est un peu froissé.
+narrateur|Raphaël le met dans la poche de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1880,12 +1959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sur le trottoir, une flaque reflète le bus. Le soleil est parti. Il reviendra, sur une autre vitre. Le doigt de Raphaël est encore frais. La poche de papa sent l'encre du ticket.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sur le trottoir, une flaque reflète le bus. Le soleil est parti. Il reviendra, sur une autre vitre. Le doigt de Raphaël est encore frais. La poche de papa sent l'encre du ticket.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1941,7 +2020,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
@@ -2020,10 +2099,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Sur le trottoir, une flaque reflète le bus.
+enfant-m|Le soleil est parti.
+papa|Il reviendra, sur une autre vitre.
+narrateur|Le doigt de Raphaël est encore frais.
+narrateur|La poche de papa sent l'encre du ticket.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2042,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2080,6 +2162,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.TRA.002-02.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.002-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>bus</t>
+          <t>bus de ville, matin humide</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hugo, papa</t>
+          <t>Raphaël, papa</t>
         </is>
       </c>
     </row>
